--- a/LISTAS_ORDENADAS/MI/Mangueras Espatulas y Articulos de goma/PARAGOLPES PARA PUERTA DISMAY.xlsx
+++ b/LISTAS_ORDENADAS/MI/Mangueras Espatulas y Articulos de goma/PARAGOLPES PARA PUERTA DISMAY.xlsx
@@ -720,14 +720,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="22" t="n">
-        <v>45182.6249980565</v>
+        <v>45266</v>
       </c>
       <c r="E1" s="5" t="n"/>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
     <row r="6" ht="22.5" customHeight="1" s="19">
       <c r="A6" s="1" t="inlineStr">
         <is>
@@ -768,25 +764,6 @@
     <row r="11" ht="41.25" customHeight="1" s="19">
       <c r="E11" s="13" t="n"/>
     </row>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
     <row r="31" ht="18" customHeight="1" s="19">
       <c r="A31" s="6" t="inlineStr">
         <is>
@@ -904,20 +881,6 @@
     <row r="38" ht="18" customHeight="1" s="19">
       <c r="E38" s="2" t="n"/>
     </row>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52"/>
     <row r="53" ht="15.75" customHeight="1" s="19">
       <c r="A53" s="3" t="n"/>
     </row>
@@ -926,15 +889,15 @@
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="A10:D10"/>
     <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="B34:C34"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>
